--- a/epiverse/data/Simulation parameters(1).xlsx
+++ b/epiverse/data/Simulation parameters(1).xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mark/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mark/Classes/Epi/Epiverse/epiverse/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8B3FE3-847B-E844-8623-2E12FF4805B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E14035-268B-FD41-9F26-8AC28136E692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1220" yWindow="500" windowWidth="16180" windowHeight="20500" activeTab="2" xr2:uid="{EDFB6D7C-8216-ED43-8AA6-178B9CD2875A}"/>
+    <workbookView xWindow="17420" yWindow="500" windowWidth="16180" windowHeight="20500" activeTab="2" xr2:uid="{EDFB6D7C-8216-ED43-8AA6-178B9CD2875A}"/>
   </bookViews>
   <sheets>
     <sheet name="Phase1" sheetId="6" r:id="rId1"/>
     <sheet name="Phase2" sheetId="2" r:id="rId2"/>
     <sheet name="Phase3" sheetId="3" r:id="rId3"/>
     <sheet name="Phase4" sheetId="5" r:id="rId4"/>
-    <sheet name="OLD" sheetId="1" r:id="rId5"/>
-    <sheet name="SB_Risk_Preeclampsia" sheetId="4" r:id="rId6"/>
+    <sheet name="Phase5" sheetId="7" r:id="rId5"/>
+    <sheet name="OLD" sheetId="1" r:id="rId6"/>
+    <sheet name="SB_Risk_Preeclampsia" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,11 +45,16 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={35C57926-D2D1-1E4D-B53B-E5E2E4FD75E7}</author>
-    <author>tc={185333BF-83E7-AF45-9DD5-668399EC57D8}</author>
-    <author>tc={5A01CF90-F8E3-6640-BC32-993409305B38}</author>
-    <author>tc={50F77D56-3B06-6E4B-8155-7833EAB9408D}</author>
+    <author>tc={9A5BA4F2-D71D-6E40-92FE-646A717AC649}</author>
+    <author>tc={AA203F26-57EB-FD4D-96A8-1E3EC58078F0}</author>
+    <author>tc={136807CB-0C11-AF4B-B455-BA7E6BADFC55}</author>
+    <author>tc={A72EBEFA-8135-284E-ADA0-30EDB9DF31E0}</author>
+    <author>tc={E0F99EF9-03C3-8340-B100-DF68AE4D4DF8}</author>
+    <author>tc={BA1965E4-CB1E-A446-858D-2C189AC85BC3}</author>
+    <author>tc={B884D584-EC30-294D-8EAD-B0E58A3378E6}</author>
+    <author>tc={AAEBD684-F7D6-6E4D-896A-3757334CE7FF}</author>
     <author>tc={73131F6C-4FDD-8242-81D0-C94D07ECA3E3}</author>
-    <author>tc={D6D95E37-6D2A-4548-AFD1-5EE5DA643221}</author>
+    <author>tc={F0934731-78BA-194A-B9CD-EC5F1F6C9CE0}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{35C57926-D2D1-1E4D-B53B-E5E2E4FD75E7}">
@@ -59,23 +65,51 @@
     https://www.medicalnewstoday.com/articles/322634#miscarriage-rates-by-week</t>
       </text>
     </comment>
-    <comment ref="B2" authorId="1" shapeId="0" xr:uid="{185333BF-83E7-AF45-9DD5-668399EC57D8}">
+    <comment ref="B2" authorId="1" shapeId="0" xr:uid="{9A5BA4F2-D71D-6E40-92FE-646A717AC649}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Originally had this as 0.5, but it was really high and lots of people not included in trial. Brought this down to 0.3. Same with gw 1</t>
+    Originally had this as 0.5, but it was really high and lots of people not included in trial. Brought this down to 0.2. Same with gw 1</t>
       </text>
     </comment>
-    <comment ref="B4" authorId="2" shapeId="0" xr:uid="{5A01CF90-F8E3-6640-BC32-993409305B38}">
+    <comment ref="B4" authorId="2" shapeId="0" xr:uid="{AA203F26-57EB-FD4D-96A8-1E3EC58078F0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Lowered this slightly from 0.2 to 0.15 to improve sample size.</t>
+    Lowered this slightly from 0.2 to 0.1 to improve sample size.</t>
       </text>
     </comment>
-    <comment ref="B21" authorId="3" shapeId="0" xr:uid="{50F77D56-3B06-6E4B-8155-7833EAB9408D}">
+    <comment ref="E4" authorId="3" shapeId="0" xr:uid="{136807CB-0C11-AF4B-B455-BA7E6BADFC55}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Previously 0 because got confused on gw from conception and from LMP
+Reply:
+    Increasing slightly so that we can increase the number of participants in the sample for now. Previously 0.1.</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="4" shapeId="0" xr:uid="{A72EBEFA-8135-284E-ADA0-30EDB9DF31E0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Previously 0 because got confused on gw from conception and from LMP
+Reply:
+    Increased slightly to increase # of participants. From 0.2 to 0.3</t>
+      </text>
+    </comment>
+    <comment ref="E20" authorId="5" shapeId="0" xr:uid="{E0F99EF9-03C3-8340-B100-DF68AE4D4DF8}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Previously 0.5. However, increased it to 1 because this is 20 gw from LMP. </t>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="6" shapeId="0" xr:uid="{BA1965E4-CB1E-A446-858D-2C189AC85BC3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -83,7 +117,23 @@
     All the 0.003s — https://stacks.cdc.gov/view/cdc/61387</t>
       </text>
     </comment>
-    <comment ref="C26" authorId="4" shapeId="0" xr:uid="{73131F6C-4FDD-8242-81D0-C94D07ECA3E3}">
+    <comment ref="E21" authorId="7" shapeId="0" xr:uid="{B884D584-EC30-294D-8EAD-B0E58A3378E6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Previously 0.5. See above</t>
+      </text>
+    </comment>
+    <comment ref="E22" authorId="8" shapeId="0" xr:uid="{AAEBD684-F7D6-6E4D-896A-3757334CE7FF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Previously 1. See above comment.</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="9" shapeId="0" xr:uid="{73131F6C-4FDD-8242-81D0-C94D07ECA3E3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -91,7 +141,7 @@
     https://www.ncbi.nlm.nih.gov/pmc/articles/PMC9847908/#:~:text=There%20was%20a%20peak%20of,%25)%20occurring%20at%2039%20weeks.</t>
       </text>
     </comment>
-    <comment ref="B37" authorId="5" shapeId="0" xr:uid="{D6D95E37-6D2A-4548-AFD1-5EE5DA643221}">
+    <comment ref="B37" authorId="10" shapeId="0" xr:uid="{F0934731-78BA-194A-B9CD-EC5F1F6C9CE0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -108,6 +158,8 @@
   <authors>
     <author>tc={2761945B-CCCA-C740-B794-13037E1324C6}</author>
     <author>tc={642DC8BF-9352-A841-B7D5-D2353D7406FD}</author>
+    <author>tc={6E365861-8AD7-9741-8A7F-D39E04493C98}</author>
+    <author>tc={34791295-B5FE-8945-B66F-FD8231C95036}</author>
     <author>tc={4C6D7E70-155D-F143-8348-12998FB8F68A}</author>
     <author>tc={0750D8B8-3F43-0249-A235-DC6D645DAACD}</author>
     <author>tc={2685FFE7-F524-DD45-9B6C-36B63629A0C0}</author>
@@ -131,7 +183,23 @@
     Values for gw 0-4 are the same because people wouldn’t actually be treated at this point, even if they entered the trial. This will be dealt with on the coding side.</t>
       </text>
     </comment>
-    <comment ref="C21" authorId="2" shapeId="0" xr:uid="{4C6D7E70-155D-F143-8348-12998FB8F68A}">
+    <comment ref="C2" authorId="2" shapeId="0" xr:uid="{6E365861-8AD7-9741-8A7F-D39E04493C98}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Originally had this as 0.5, but it was really high and lots of people not included in trial. Brought this down to 0.2. Same with gw 1</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="3" shapeId="0" xr:uid="{34791295-B5FE-8945-B66F-FD8231C95036}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Lowered this slightly from 0.2 to 0.1 to improve sample size.</t>
+      </text>
+    </comment>
+    <comment ref="C21" authorId="4" shapeId="0" xr:uid="{4C6D7E70-155D-F143-8348-12998FB8F68A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -139,15 +207,17 @@
     All the 0.003s — https://stacks.cdc.gov/view/cdc/61387</t>
       </text>
     </comment>
-    <comment ref="D26" authorId="3" shapeId="0" xr:uid="{0750D8B8-3F43-0249-A235-DC6D645DAACD}">
+    <comment ref="D26" authorId="5" shapeId="0" xr:uid="{0750D8B8-3F43-0249-A235-DC6D645DAACD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    https://www.ncbi.nlm.nih.gov/pmc/articles/PMC9847908/#:~:text=There%20was%20a%20peak%20of,%25)%20occurring%20at%2039%20weeks.</t>
+    https://www.ncbi.nlm.nih.gov/pmc/articles/PMC9847908/#:~:text=There%20was%20a%20peak%20of,%25)%20occurring%20at%2039%20weeks.
+Reply:
+    Going to have it decrease the risk of preterm birth</t>
       </text>
     </comment>
-    <comment ref="C37" authorId="4" shapeId="0" xr:uid="{2685FFE7-F524-DD45-9B6C-36B63629A0C0}">
+    <comment ref="C37" authorId="6" shapeId="0" xr:uid="{2685FFE7-F524-DD45-9B6C-36B63629A0C0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -330,7 +400,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
     <t>p_fetaldeath</t>
   </si>
@@ -436,6 +506,9 @@
   <si>
     <t>p_preeclampsia_original</t>
   </si>
+  <si>
+    <t>p_censoring</t>
+  </si>
 </sst>
 </file>
 
@@ -497,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -508,7 +581,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -832,19 +904,40 @@
   <threadedComment ref="B1" dT="2023-10-20T20:28:15.91" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{35C57926-D2D1-1E4D-B53B-E5E2E4FD75E7}">
     <text>https://www.medicalnewstoday.com/articles/322634#miscarriage-rates-by-week</text>
   </threadedComment>
-  <threadedComment ref="B2" dT="2023-11-27T01:39:00.90" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{185333BF-83E7-AF45-9DD5-668399EC57D8}">
-    <text>Originally had this as 0.5, but it was really high and lots of people not included in trial. Brought this down to 0.3. Same with gw 1</text>
+  <threadedComment ref="B2" dT="2023-11-27T01:39:00.90" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{9A5BA4F2-D71D-6E40-92FE-646A717AC649}">
+    <text>Originally had this as 0.5, but it was really high and lots of people not included in trial. Brought this down to 0.2. Same with gw 1</text>
   </threadedComment>
-  <threadedComment ref="B4" dT="2023-11-27T01:41:40.99" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{5A01CF90-F8E3-6640-BC32-993409305B38}">
-    <text>Lowered this slightly from 0.2 to 0.15 to improve sample size.</text>
+  <threadedComment ref="B4" dT="2023-11-27T01:41:40.99" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{AA203F26-57EB-FD4D-96A8-1E3EC58078F0}">
+    <text>Lowered this slightly from 0.2 to 0.1 to improve sample size.</text>
   </threadedComment>
-  <threadedComment ref="B21" dT="2023-10-20T20:32:56.90" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{50F77D56-3B06-6E4B-8155-7833EAB9408D}">
+  <threadedComment ref="E4" dT="2023-12-15T18:58:17.41" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{136807CB-0C11-AF4B-B455-BA7E6BADFC55}">
+    <text>Previously 0 because got confused on gw from conception and from LMP</text>
+  </threadedComment>
+  <threadedComment ref="E4" dT="2024-01-02T16:11:10.95" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{3D49A58A-FD00-2148-8526-B40661E9E107}" parentId="{136807CB-0C11-AF4B-B455-BA7E6BADFC55}">
+    <text>Increasing slightly so that we can increase the number of participants in the sample for now. Previously 0.1.</text>
+  </threadedComment>
+  <threadedComment ref="E5" dT="2023-12-15T18:58:17.41" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{A72EBEFA-8135-284E-ADA0-30EDB9DF31E0}">
+    <text>Previously 0 because got confused on gw from conception and from LMP</text>
+  </threadedComment>
+  <threadedComment ref="E5" dT="2024-01-02T16:11:31.32" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{ACF83317-8955-5743-AA16-ADD357B2BB13}" parentId="{A72EBEFA-8135-284E-ADA0-30EDB9DF31E0}">
+    <text>Increased slightly to increase # of participants. From 0.2 to 0.3</text>
+  </threadedComment>
+  <threadedComment ref="E20" dT="2023-12-15T18:59:01.95" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{E0F99EF9-03C3-8340-B100-DF68AE4D4DF8}">
+    <text xml:space="preserve">Previously 0.5. However, increased it to 1 because this is 20 gw from LMP. </text>
+  </threadedComment>
+  <threadedComment ref="B21" dT="2023-10-20T20:32:56.90" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{BA1965E4-CB1E-A446-858D-2C189AC85BC3}">
     <text>All the 0.003s — https://stacks.cdc.gov/view/cdc/61387</text>
+  </threadedComment>
+  <threadedComment ref="E21" dT="2023-12-15T18:59:16.45" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{B884D584-EC30-294D-8EAD-B0E58A3378E6}">
+    <text>Previously 0.5. See above</text>
+  </threadedComment>
+  <threadedComment ref="E22" dT="2023-12-15T18:59:30.81" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{AAEBD684-F7D6-6E4D-896A-3757334CE7FF}">
+    <text>Previously 1. See above comment.</text>
   </threadedComment>
   <threadedComment ref="C26" dT="2023-10-20T20:36:59.95" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{73131F6C-4FDD-8242-81D0-C94D07ECA3E3}">
     <text>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC9847908/#:~:text=There%20was%20a%20peak%20of,%25)%20occurring%20at%2039%20weeks.</text>
   </threadedComment>
-  <threadedComment ref="B37" dT="2023-10-20T20:29:33.53" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{D6D95E37-6D2A-4548-AFD1-5EE5DA643221}">
+  <threadedComment ref="B37" dT="2023-10-20T20:29:33.53" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{F0934731-78BA-194A-B9CD-EC5F1F6C9CE0}">
     <text>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC3719843/#:~:text=The%20risk%20of%20stillbirth%20at,at%2042%20weeks%20of%20gestation.</text>
   </threadedComment>
 </ThreadedComments>
@@ -861,11 +954,20 @@
   <threadedComment ref="A2" dT="2023-11-25T18:21:45.43" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{642DC8BF-9352-A841-B7D5-D2353D7406FD}">
     <text>Values for gw 0-4 are the same because people wouldn’t actually be treated at this point, even if they entered the trial. This will be dealt with on the coding side.</text>
   </threadedComment>
+  <threadedComment ref="C2" dT="2023-11-27T01:39:00.90" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{6E365861-8AD7-9741-8A7F-D39E04493C98}">
+    <text>Originally had this as 0.5, but it was really high and lots of people not included in trial. Brought this down to 0.2. Same with gw 1</text>
+  </threadedComment>
+  <threadedComment ref="C4" dT="2023-11-27T01:41:40.99" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{34791295-B5FE-8945-B66F-FD8231C95036}">
+    <text>Lowered this slightly from 0.2 to 0.1 to improve sample size.</text>
+  </threadedComment>
   <threadedComment ref="C21" dT="2023-10-20T20:32:56.90" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{4C6D7E70-155D-F143-8348-12998FB8F68A}">
     <text>All the 0.003s — https://stacks.cdc.gov/view/cdc/61387</text>
   </threadedComment>
   <threadedComment ref="D26" dT="2023-10-20T20:36:59.95" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{0750D8B8-3F43-0249-A235-DC6D645DAACD}">
     <text>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC9847908/#:~:text=There%20was%20a%20peak%20of,%25)%20occurring%20at%2039%20weeks.</text>
+  </threadedComment>
+  <threadedComment ref="D26" dT="2023-12-15T03:39:36.56" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{D51B01E8-6637-E44B-A544-4E4553ED1B10}" parentId="{0750D8B8-3F43-0249-A235-DC6D645DAACD}">
+    <text>Going to have it decrease the risk of preterm birth</text>
   </threadedComment>
   <threadedComment ref="C37" dT="2023-10-20T20:29:33.53" personId="{51D2B8DB-A2F5-4646-800E-4DB3664DB2F8}" id="{2685FFE7-F524-DD45-9B6C-36B63629A0C0}">
     <text>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC3719843/#:~:text=The%20risk%20of%20stillbirth%20at,at%2042%20weeks%20of%20gestation.</text>
@@ -991,14 +1093,14 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
         <f>1-C2-B2</f>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1009,14 +1111,14 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D6" si="0">1-C3-B3</f>
-        <v>0.7</v>
+        <f>1-C3-B3</f>
+        <v>0.8</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1027,17 +1129,17 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
-        <v>0.85</v>
+        <f>1-C4-B4</f>
+        <v>0.9</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1045,17 +1147,17 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <f t="shared" si="0"/>
-        <v>0.85</v>
+        <f>1-C5-B5</f>
+        <v>0.9</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1069,11 +1171,11 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <f t="shared" si="0"/>
+        <f>1-C6-B6</f>
         <v>0.95</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1087,11 +1189,11 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <f t="shared" ref="D7:D41" si="1">1-B7-C7</f>
+        <f t="shared" ref="D7:D41" si="0">1-B7-C7</f>
         <v>0.95</v>
       </c>
       <c r="E7">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1105,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.97</v>
       </c>
       <c r="E8">
@@ -1123,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.97</v>
       </c>
       <c r="E9">
@@ -1141,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.97</v>
       </c>
       <c r="E10">
@@ -1159,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.97</v>
       </c>
       <c r="E11">
@@ -1177,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.97</v>
       </c>
       <c r="E12">
@@ -1195,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.97</v>
       </c>
       <c r="E13">
@@ -1213,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
       <c r="E14">
@@ -1231,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
       <c r="E15">
@@ -1249,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
       <c r="E16">
@@ -1267,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
       <c r="E17">
@@ -1285,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
       <c r="E18">
@@ -1303,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
       <c r="E19">
@@ -1321,11 +1423,11 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
       <c r="E20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1339,11 +1441,11 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.997</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -1357,11 +1459,11 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.997</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1375,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.997</v>
       </c>
       <c r="E23">
@@ -1393,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.997</v>
       </c>
       <c r="E24">
@@ -1411,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.997</v>
       </c>
       <c r="E25">
@@ -1429,7 +1531,7 @@
         <v>0.01</v>
       </c>
       <c r="D26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.98699999999999999</v>
       </c>
       <c r="E26">
@@ -1447,7 +1549,7 @@
         <v>0.01</v>
       </c>
       <c r="D27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.98699999999999999</v>
       </c>
       <c r="E27">
@@ -1465,7 +1567,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.98199999999999998</v>
       </c>
       <c r="E28">
@@ -1483,7 +1585,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.98199999999999998</v>
       </c>
       <c r="E29">
@@ -1501,7 +1603,7 @@
         <v>0.02</v>
       </c>
       <c r="D30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.97699999999999998</v>
       </c>
       <c r="E30">
@@ -1519,7 +1621,7 @@
         <v>0.02</v>
       </c>
       <c r="D31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.97699999999999998</v>
       </c>
       <c r="E31">
@@ -1537,7 +1639,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.97199999999999998</v>
       </c>
       <c r="E32">
@@ -1555,7 +1657,7 @@
         <v>0.03</v>
       </c>
       <c r="D33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.96699999999999997</v>
       </c>
       <c r="E33">
@@ -1573,7 +1675,7 @@
         <v>0.09</v>
       </c>
       <c r="D34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.90700000000000003</v>
       </c>
       <c r="E34">
@@ -1591,7 +1693,7 @@
         <v>0.09</v>
       </c>
       <c r="D35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.90700000000000003</v>
       </c>
       <c r="E35">
@@ -1609,7 +1711,7 @@
         <v>0.09</v>
       </c>
       <c r="D36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.90700000000000003</v>
       </c>
       <c r="E36">
@@ -1628,7 +1730,7 @@
         <v>0.3</v>
       </c>
       <c r="D37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.69978999999999991</v>
       </c>
       <c r="E37">
@@ -1646,7 +1748,7 @@
         <v>0.35</v>
       </c>
       <c r="D38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.64973000000000003</v>
       </c>
       <c r="E38">
@@ -1664,7 +1766,7 @@
         <v>0.7</v>
       </c>
       <c r="D39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.29965000000000008</v>
       </c>
       <c r="E39">
@@ -1682,7 +1784,7 @@
         <v>0.7</v>
       </c>
       <c r="D40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.29958000000000007</v>
       </c>
       <c r="E40">
@@ -1700,7 +1802,7 @@
         <v>0.7</v>
       </c>
       <c r="D41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.29939000000000004</v>
       </c>
       <c r="E41">
@@ -1768,14 +1870,14 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
         <f>1-D2-C2</f>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1786,14 +1888,14 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E5" si="0">1-D3-C3</f>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1804,14 +1906,14 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1822,14 +1924,14 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -2224,11 +2326,12 @@
         <v>2.4000000000000002E-3</v>
       </c>
       <c r="D26">
-        <v>0.01</v>
+        <f>0.7*Phase1!C26</f>
+        <v>6.9999999999999993E-3</v>
       </c>
       <c r="E26">
         <f t="shared" si="2"/>
-        <v>0.98760000000000003</v>
+        <v>0.99060000000000004</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -2243,11 +2346,12 @@
         <v>2.4000000000000002E-3</v>
       </c>
       <c r="D27">
-        <v>0.01</v>
+        <f>0.7*Phase1!C27</f>
+        <v>6.9999999999999993E-3</v>
       </c>
       <c r="E27">
         <f t="shared" si="2"/>
-        <v>0.98760000000000003</v>
+        <v>0.99060000000000004</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -2262,11 +2366,12 @@
         <v>2.4000000000000002E-3</v>
       </c>
       <c r="D28">
-        <v>1.4999999999999999E-2</v>
+        <f>0.7*Phase1!C28</f>
+        <v>1.0499999999999999E-2</v>
       </c>
       <c r="E28">
         <f t="shared" si="2"/>
-        <v>0.98260000000000003</v>
+        <v>0.98710000000000009</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -2281,11 +2386,12 @@
         <v>2.4000000000000002E-3</v>
       </c>
       <c r="D29">
-        <v>1.4999999999999999E-2</v>
+        <f>0.7*Phase1!C29</f>
+        <v>1.0499999999999999E-2</v>
       </c>
       <c r="E29">
         <f t="shared" si="2"/>
-        <v>0.98260000000000003</v>
+        <v>0.98710000000000009</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -2300,11 +2406,12 @@
         <v>2.4000000000000002E-3</v>
       </c>
       <c r="D30">
-        <v>0.02</v>
+        <f>0.7*Phase1!C30</f>
+        <v>1.3999999999999999E-2</v>
       </c>
       <c r="E30">
         <f t="shared" si="2"/>
-        <v>0.97760000000000002</v>
+        <v>0.98360000000000003</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -2319,11 +2426,12 @@
         <v>2.4000000000000002E-3</v>
       </c>
       <c r="D31">
-        <v>0.02</v>
+        <f>0.7*Phase1!C31</f>
+        <v>1.3999999999999999E-2</v>
       </c>
       <c r="E31">
         <f t="shared" si="2"/>
-        <v>0.97760000000000002</v>
+        <v>0.98360000000000003</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -2338,11 +2446,12 @@
         <v>2.4000000000000002E-3</v>
       </c>
       <c r="D32">
-        <v>2.5000000000000001E-2</v>
+        <f>0.7*Phase1!C32</f>
+        <v>1.7499999999999998E-2</v>
       </c>
       <c r="E32">
         <f t="shared" si="2"/>
-        <v>0.97260000000000002</v>
+        <v>0.98010000000000008</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -2357,11 +2466,12 @@
         <v>2.4000000000000002E-3</v>
       </c>
       <c r="D33">
-        <v>0.03</v>
+        <f>0.7*Phase1!C33</f>
+        <v>2.0999999999999998E-2</v>
       </c>
       <c r="E33">
         <f t="shared" si="2"/>
-        <v>0.96760000000000002</v>
+        <v>0.97660000000000002</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -2376,11 +2486,12 @@
         <v>2.4000000000000002E-3</v>
       </c>
       <c r="D34">
-        <v>0.09</v>
+        <f>0.7*Phase1!C34</f>
+        <v>6.3E-2</v>
       </c>
       <c r="E34">
         <f t="shared" si="2"/>
-        <v>0.90760000000000007</v>
+        <v>0.9346000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -2395,11 +2506,12 @@
         <v>2.4000000000000002E-3</v>
       </c>
       <c r="D35">
-        <v>0.09</v>
+        <f>0.7*Phase1!C35</f>
+        <v>6.3E-2</v>
       </c>
       <c r="E35">
         <f t="shared" si="2"/>
-        <v>0.90760000000000007</v>
+        <v>0.9346000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -2414,11 +2526,12 @@
         <v>2.4000000000000002E-3</v>
       </c>
       <c r="D36">
-        <v>0.09</v>
+        <f>0.7*Phase1!C36</f>
+        <v>6.3E-2</v>
       </c>
       <c r="E36">
         <f t="shared" si="2"/>
-        <v>0.90760000000000007</v>
+        <v>0.9346000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -2433,11 +2546,12 @@
         <v>1.6800000000000002E-4</v>
       </c>
       <c r="D37">
-        <v>0.3</v>
+        <f>0.7*Phase1!C37</f>
+        <v>0.21</v>
       </c>
       <c r="E37">
         <f t="shared" si="2"/>
-        <v>0.69983200000000001</v>
+        <v>0.78983200000000009</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -2452,11 +2566,12 @@
         <v>2.1600000000000002E-4</v>
       </c>
       <c r="D38">
-        <v>0.35</v>
+        <f>0.7*Phase1!C38</f>
+        <v>0.24499999999999997</v>
       </c>
       <c r="E38">
         <f t="shared" si="2"/>
-        <v>0.64978400000000003</v>
+        <v>0.75478400000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -2470,12 +2585,13 @@
         <f>0.8*Phase1!B39</f>
         <v>2.8000000000000003E-4</v>
       </c>
-      <c r="D39">
-        <v>0.7</v>
+      <c r="D39" s="5">
+        <f>1.05*Phase1!C39</f>
+        <v>0.73499999999999999</v>
       </c>
       <c r="E39">
         <f t="shared" si="2"/>
-        <v>0.2997200000000001</v>
+        <v>0.26472000000000007</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -2489,12 +2605,13 @@
         <f>0.8*Phase1!B40</f>
         <v>3.3600000000000004E-4</v>
       </c>
-      <c r="D40">
-        <v>0.7</v>
+      <c r="D40" s="5">
+        <f>1.05*Phase1!C40</f>
+        <v>0.73499999999999999</v>
       </c>
       <c r="E40">
         <f t="shared" si="2"/>
-        <v>0.29966400000000004</v>
+        <v>0.26466400000000001</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -2508,12 +2625,13 @@
         <f>0.8*Phase1!B41</f>
         <v>4.8799999999999999E-4</v>
       </c>
-      <c r="D41">
-        <v>0.7</v>
+      <c r="D41" s="5">
+        <f>1.05*Phase1!C41</f>
+        <v>0.73499999999999999</v>
       </c>
       <c r="E41">
         <f t="shared" si="2"/>
-        <v>0.299512</v>
+        <v>0.26451199999999997</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -2543,7 +2661,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CCEC42C-213B-4245-8F9C-C0F65FBC0D09}">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -2584,1039 +2702,516 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f>10*B2</f>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D2">
+        <f>LN(C2/(1-C2))</f>
+        <v>-5.5174528964647074</v>
       </c>
       <c r="E2">
         <v>0.6</v>
       </c>
       <c r="F2">
-        <f t="shared" ref="F2:F25" si="0">LN(E2)</f>
+        <f>LN(E2)</f>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="H2">
+        <f t="shared" ref="H2:H18" si="0">1-G2</f>
+        <v>0.98299999999999998</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" ref="C3:C18" si="1">10*B3</f>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D3">
+        <f>LN(C3/(1-C3))</f>
+        <v>-5.5174528964647074</v>
       </c>
       <c r="E3">
         <v>0.6</v>
       </c>
       <c r="F3">
-        <f t="shared" si="0"/>
+        <f>LN(E3)</f>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="0"/>
+        <v>0.98299999999999998</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D18" si="2">LN(C4/(1-C4))</f>
+        <v>-5.2933048247244923</v>
       </c>
       <c r="E4">
         <v>0.6</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F4:F18" si="3">LN(E4)</f>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>0.997</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>5.9999999999999993E-3</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>-5.1099777374285189</v>
       </c>
       <c r="E5">
         <v>0.6</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>0.996</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="2"/>
+        <v>-4.9548205149898594</v>
       </c>
       <c r="E6">
         <v>0.6</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>0.997</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="2"/>
+        <v>-4.8202815656050371</v>
       </c>
       <c r="E7">
         <v>0.6</v>
       </c>
       <c r="F7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>0.997</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="2"/>
+        <v>-4.7014899569937691</v>
       </c>
       <c r="E8">
         <v>0.6</v>
       </c>
       <c r="F8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>0.997</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>0.01</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="2"/>
+        <v>-4.5951198501345898</v>
       </c>
       <c r="E9">
         <v>0.6</v>
       </c>
       <c r="F9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>0.997</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1.8E-3</v>
       </c>
       <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="2"/>
+        <v>-3.9992195504583012</v>
       </c>
       <c r="E10">
         <v>0.6</v>
       </c>
       <c r="F10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>0.997</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>2E-3</v>
       </c>
       <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="2"/>
+        <v>-3.8918202981106265</v>
       </c>
       <c r="E11">
         <v>0.6</v>
       </c>
       <c r="F11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>0.997</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="2"/>
+        <v>-3.1780538303479453</v>
       </c>
       <c r="E12">
         <v>0.6</v>
       </c>
       <c r="F12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>0.997</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="2"/>
+        <v>-2.9444389791664403</v>
       </c>
       <c r="E13">
         <v>0.6</v>
       </c>
       <c r="F13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13">
+        <v>1E-3</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>0.999</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="2"/>
+        <v>-2.5866893440979424</v>
       </c>
       <c r="E14">
         <v>0.6</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14">
+        <v>1E-3</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>0.999</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>0.08</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="2"/>
+        <v>-2.4423470353692043</v>
       </c>
       <c r="E15">
         <v>0.6</v>
       </c>
       <c r="F15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15">
+        <v>1E-3</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>0.999</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="2"/>
+        <v>-4.7014899569937691</v>
       </c>
       <c r="E16">
         <v>0.6</v>
       </c>
       <c r="F16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16">
+        <v>1E-3</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>0.999</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>-2.0907410969337694</v>
       </c>
       <c r="E17">
         <v>0.6</v>
       </c>
       <c r="F17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17">
+        <v>2E-3</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>0.998</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1.4E-2</v>
       </c>
       <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8">
-        <v>-1.0000000000000001E+50</v>
+        <f t="shared" si="1"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="2"/>
+        <v>-1.8152899666382492</v>
       </c>
       <c r="E18">
         <v>0.6</v>
       </c>
       <c r="F18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.51082562376599072</v>
       </c>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19" s="8">
-        <v>-1.0000000000000001E+50</v>
-      </c>
-      <c r="E19">
-        <v>0.6</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="0"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20" s="8">
-        <v>-1.0000000000000001E+50</v>
-      </c>
-      <c r="E20">
-        <v>0.6</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="0"/>
-        <v>-0.51082562376599072</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8">
-        <v>-1.0000000000000001E+50</v>
-      </c>
-      <c r="E21">
-        <v>0.6</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="0"/>
-        <v>-0.51082562376599072</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22" s="8">
-        <v>-1.0000000000000001E+50</v>
-      </c>
-      <c r="E22">
-        <v>0.6</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="0"/>
-        <v>-0.51082562376599072</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23" s="8">
-        <v>-1.0000000000000001E+50</v>
-      </c>
-      <c r="E23">
-        <v>0.6</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="0"/>
-        <v>-0.51082562376599072</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24" s="8">
-        <v>-1.0000000000000001E+50</v>
-      </c>
-      <c r="E24">
-        <v>0.6</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="0"/>
-        <v>-0.51082562376599072</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25" s="8">
-        <v>-1.0000000000000001E+50</v>
-      </c>
-      <c r="E25">
-        <v>0.6</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="0"/>
-        <v>-0.51082562376599072</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="C26">
-        <f>15*B26</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="D26">
-        <f>LN(C26/(1-C26))</f>
-        <v>-5.1099777374285189</v>
-      </c>
-      <c r="E26">
-        <v>0.6</v>
-      </c>
-      <c r="F26">
-        <f>LN(E26)</f>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G26">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="H26">
-        <f t="shared" ref="H26:H42" si="1">1-G26</f>
-        <v>0.98299999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="C27">
-        <f>15*B27</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="D27">
-        <f>LN(C27/(1-C27))</f>
-        <v>-5.1099777374285189</v>
-      </c>
-      <c r="E27">
-        <v>0.6</v>
-      </c>
-      <c r="F27">
-        <f>LN(E27)</f>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G27">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="H27">
-        <f t="shared" si="1"/>
-        <v>0.98299999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="C28">
-        <f t="shared" ref="C28:C42" si="2">15*B28</f>
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="D28">
-        <f t="shared" ref="D28:D42" si="3">LN(C28/(1-C28))</f>
-        <v>-4.8853239920190807</v>
-      </c>
-      <c r="E28">
-        <v>0.6</v>
-      </c>
-      <c r="F28">
-        <f t="shared" ref="F28:F42" si="4">LN(E28)</f>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G28">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H28">
-        <f t="shared" si="1"/>
-        <v>0.997</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="C29">
-        <f t="shared" si="2"/>
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="D29">
-        <f t="shared" si="3"/>
-        <v>-4.7014899569937691</v>
-      </c>
-      <c r="E29">
-        <v>0.6</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G29">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H29">
-        <f t="shared" si="1"/>
-        <v>0.996</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="C30">
-        <f t="shared" si="2"/>
-        <v>1.0500000000000001E-2</v>
-      </c>
-      <c r="D30">
-        <f t="shared" si="3"/>
-        <v>-4.5458245078791428</v>
-      </c>
-      <c r="E30">
-        <v>0.6</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G30">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H30">
-        <f t="shared" si="1"/>
-        <v>0.997</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="C31">
-        <f t="shared" si="2"/>
-        <v>1.2E-2</v>
-      </c>
-      <c r="D31">
-        <f t="shared" si="3"/>
-        <v>-4.4107760479598674</v>
-      </c>
-      <c r="E31">
-        <v>0.6</v>
-      </c>
-      <c r="F31">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G31">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H31">
-        <f t="shared" si="1"/>
-        <v>0.997</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="B32">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="C32">
-        <f t="shared" si="2"/>
-        <v>1.35E-2</v>
-      </c>
-      <c r="D32">
-        <f t="shared" si="3"/>
-        <v>-4.2914736400182862</v>
-      </c>
-      <c r="E32">
-        <v>0.6</v>
-      </c>
-      <c r="F32">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G32">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H32">
-        <f t="shared" si="1"/>
-        <v>0.997</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="B33">
+      <c r="G18">
         <v>1E-3</v>
       </c>
-      <c r="C33">
-        <f t="shared" si="2"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D33">
-        <f t="shared" si="3"/>
-        <v>-4.1845914400698785</v>
-      </c>
-      <c r="E33">
-        <v>0.6</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G33">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H33">
-        <f t="shared" si="1"/>
-        <v>0.997</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>32</v>
-      </c>
-      <c r="B34">
-        <v>1.8E-3</v>
-      </c>
-      <c r="C34">
-        <f t="shared" si="2"/>
-        <v>2.7E-2</v>
-      </c>
-      <c r="D34">
-        <f t="shared" si="3"/>
-        <v>-3.5845472161816758</v>
-      </c>
-      <c r="E34">
-        <v>0.6</v>
-      </c>
-      <c r="F34">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G34">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H34">
-        <f t="shared" si="1"/>
-        <v>0.997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="B35">
-        <v>2E-3</v>
-      </c>
-      <c r="C35">
-        <f t="shared" si="2"/>
-        <v>0.03</v>
-      </c>
-      <c r="D35">
-        <f t="shared" si="3"/>
-        <v>-3.4760986898352733</v>
-      </c>
-      <c r="E35">
-        <v>0.6</v>
-      </c>
-      <c r="F35">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G35">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H35">
-        <f t="shared" si="1"/>
-        <v>0.997</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C36">
-        <f t="shared" si="2"/>
-        <v>0.06</v>
-      </c>
-      <c r="D36">
-        <f t="shared" si="3"/>
-        <v>-2.7515353130419489</v>
-      </c>
-      <c r="E36">
-        <v>0.6</v>
-      </c>
-      <c r="F36">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G36">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H36">
-        <f t="shared" si="1"/>
-        <v>0.997</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>35</v>
-      </c>
-      <c r="B37">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C37">
-        <f t="shared" si="2"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="D37">
-        <f t="shared" si="3"/>
-        <v>-2.5123056239761148</v>
-      </c>
-      <c r="E37">
-        <v>0.6</v>
-      </c>
-      <c r="F37">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G37">
-        <v>1E-3</v>
-      </c>
-      <c r="H37">
-        <f t="shared" si="1"/>
-        <v>0.999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="B38">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="C38">
-        <f t="shared" si="2"/>
-        <v>0.105</v>
-      </c>
-      <c r="D38">
-        <f t="shared" si="3"/>
-        <v>-2.1428633681173319</v>
-      </c>
-      <c r="E38">
-        <v>0.6</v>
-      </c>
-      <c r="F38">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G38">
-        <v>1E-3</v>
-      </c>
-      <c r="H38">
-        <f t="shared" si="1"/>
-        <v>0.999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="B39">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="C39">
-        <f t="shared" si="2"/>
-        <v>0.12</v>
-      </c>
-      <c r="D39">
-        <f t="shared" si="3"/>
-        <v>-1.9924301646902063</v>
-      </c>
-      <c r="E39">
-        <v>0.6</v>
-      </c>
-      <c r="F39">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G39">
-        <v>1E-3</v>
-      </c>
-      <c r="H39">
-        <f t="shared" si="1"/>
-        <v>0.999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="B40">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="C40">
-        <f t="shared" si="2"/>
-        <v>1.35E-2</v>
-      </c>
-      <c r="D40">
-        <f t="shared" si="3"/>
-        <v>-4.2914736400182862</v>
-      </c>
-      <c r="E40">
-        <v>0.6</v>
-      </c>
-      <c r="F40">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G40">
-        <v>1E-3</v>
-      </c>
-      <c r="H40">
-        <f t="shared" si="1"/>
-        <v>0.999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>39</v>
-      </c>
-      <c r="B41">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="C41">
-        <f t="shared" si="2"/>
-        <v>0.16499999999999998</v>
-      </c>
-      <c r="D41">
-        <f t="shared" si="3"/>
-        <v>-1.621486250950275</v>
-      </c>
-      <c r="E41">
-        <v>0.6</v>
-      </c>
-      <c r="F41">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G41">
-        <v>2E-3</v>
-      </c>
-      <c r="H41">
-        <f t="shared" si="1"/>
-        <v>0.998</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>40</v>
-      </c>
-      <c r="B42">
-        <v>1.4E-2</v>
-      </c>
-      <c r="C42">
-        <f t="shared" si="2"/>
-        <v>0.21</v>
-      </c>
-      <c r="D42">
-        <f t="shared" si="3"/>
-        <v>-1.3249254147435987</v>
-      </c>
-      <c r="E42">
-        <v>0.6</v>
-      </c>
-      <c r="F42">
-        <f t="shared" si="4"/>
-        <v>-0.51082562376599072</v>
-      </c>
-      <c r="G42">
-        <v>1E-3</v>
-      </c>
-      <c r="H42">
-        <f t="shared" si="1"/>
+      <c r="H18">
+        <f t="shared" si="0"/>
         <v>0.999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3649,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -3661,7 +3256,7 @@
       </c>
       <c r="C3">
         <f>1.25*C2</f>
-        <v>0.125</v>
+        <v>0.15625</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3672,8 +3267,8 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <f>0.9*C2</f>
-        <v>9.0000000000000011E-2</v>
+        <f>0.8*C2</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -3684,8 +3279,8 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <f>0.9*1.25*C2</f>
-        <v>0.1125</v>
+        <f>0.8*C3</f>
+        <v>0.125</v>
       </c>
     </row>
   </sheetData>
@@ -3695,6 +3290,356 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{638C0E0C-D6E1-F442-8735-4FA62BD9AC1D}">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADFC6947-DBBF-D243-8019-94691EC417BF}">
   <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4508,7 +4453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0657A824-9110-B347-821D-B64D54D407AE}">
   <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5395,15 +5340,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F311363ECB49C45BE6A1ABA8AA4E3C9" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bcab42b681813b96043c0b869577973d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7962a6ab-b148-4fb3-9b24-47c6fd02e414" xmlns:ns3="78c38721-2d96-443e-bd32-82c62d4eed8a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b36b52368701cf0b88ba8d42da5a3441" ns2:_="" ns3:_="">
     <xsd:import namespace="7962a6ab-b148-4fb3-9b24-47c6fd02e414"/>
@@ -5628,15 +5564,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FC4DEEE-E4C1-4BDA-9F3A-10B42714F00A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDB1F164-DDC9-4622-8588-A1C1F4AFED79}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5653,4 +5590,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FC4DEEE-E4C1-4BDA-9F3A-10B42714F00A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>